--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/60.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/60.xlsx
@@ -426,13 +426,13 @@
         <v>-12.71855442775014</v>
       </c>
       <c r="E2">
-        <v>-7.907464892311312</v>
+        <v>-9.372172639248243</v>
       </c>
       <c r="F2">
-        <v>-0.5770566190182965</v>
+        <v>-1.028852342342161</v>
       </c>
       <c r="G2">
-        <v>-15.82724100009345</v>
+        <v>-18.89508713533513</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-12.1765769235014</v>
       </c>
       <c r="E3">
-        <v>-7.649251304393948</v>
+        <v>-9.299880080189793</v>
       </c>
       <c r="F3">
-        <v>0.1167516112378602</v>
+        <v>-1.100220335930352</v>
       </c>
       <c r="G3">
-        <v>-15.13498440928584</v>
+        <v>-18.26420474828007</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.59052448882105</v>
       </c>
       <c r="E4">
-        <v>-7.779490216854548</v>
+        <v>-9.655618884336345</v>
       </c>
       <c r="F4">
-        <v>-0.20470878492953</v>
+        <v>-0.973372435539664</v>
       </c>
       <c r="G4">
-        <v>-14.87420777133914</v>
+        <v>-18.77549533300173</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.04887578423559</v>
       </c>
       <c r="E5">
-        <v>-8.476404252738984</v>
+        <v>-10.62002535137986</v>
       </c>
       <c r="F5">
-        <v>-0.008401449446700338</v>
+        <v>-0.7275469534522855</v>
       </c>
       <c r="G5">
-        <v>-14.87967348202448</v>
+        <v>-17.98300204435607</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-10.54175324827607</v>
       </c>
       <c r="E6">
-        <v>-9.584286361767523</v>
+        <v>-11.41699149198977</v>
       </c>
       <c r="F6">
-        <v>0.07252093376538056</v>
+        <v>-0.2957289667817369</v>
       </c>
       <c r="G6">
-        <v>-13.82866796858098</v>
+        <v>-17.99304458424945</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-10.09679579771063</v>
       </c>
       <c r="E7">
-        <v>-10.83499201252397</v>
+        <v>-11.78083173613604</v>
       </c>
       <c r="F7">
-        <v>0.3636191795179604</v>
+        <v>-0.2458852717878878</v>
       </c>
       <c r="G7">
-        <v>-13.49854533322316</v>
+        <v>-17.05114803068924</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-9.718786151709294</v>
       </c>
       <c r="E8">
-        <v>-11.65054301046136</v>
+        <v>-12.24853706012225</v>
       </c>
       <c r="F8">
-        <v>0.7183244446619031</v>
+        <v>-0.5282583236867805</v>
       </c>
       <c r="G8">
-        <v>-13.03738302905715</v>
+        <v>-16.88963644546482</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-9.417966363756261</v>
       </c>
       <c r="E9">
-        <v>-12.59914510321811</v>
+        <v>-13.12101550481006</v>
       </c>
       <c r="F9">
-        <v>1.004467396610936</v>
+        <v>0.07237431273508506</v>
       </c>
       <c r="G9">
-        <v>-12.26858165956328</v>
+        <v>-16.20614121342689</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.208678402178142</v>
       </c>
       <c r="E10">
-        <v>-14.444040885469</v>
+        <v>-14.06378039457092</v>
       </c>
       <c r="F10">
-        <v>0.6565837370290476</v>
+        <v>0.101242088355245</v>
       </c>
       <c r="G10">
-        <v>-11.89381797288116</v>
+        <v>-15.71228727206057</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.087552342121031</v>
       </c>
       <c r="E11">
-        <v>-13.78524301530713</v>
+        <v>-14.30796024153851</v>
       </c>
       <c r="F11">
-        <v>0.7564575096823756</v>
+        <v>0.07126927061975051</v>
       </c>
       <c r="G11">
-        <v>-11.74403233995684</v>
+        <v>-15.58873109144389</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.075474805874469</v>
       </c>
       <c r="E12">
-        <v>-14.88156393019408</v>
+        <v>-15.42196484742542</v>
       </c>
       <c r="F12">
-        <v>0.6789339179239811</v>
+        <v>0.2874284309106703</v>
       </c>
       <c r="G12">
-        <v>-11.11754139155962</v>
+        <v>-15.10829479114824</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-9.159805535356341</v>
       </c>
       <c r="E13">
-        <v>-15.47444986117432</v>
+        <v>-16.21500027259667</v>
       </c>
       <c r="F13">
-        <v>0.4473455863885177</v>
+        <v>0.4004459091442181</v>
       </c>
       <c r="G13">
-        <v>-11.69219912844847</v>
+        <v>-14.03154316504583</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-9.352025312043855</v>
       </c>
       <c r="E14">
-        <v>-14.64542665306411</v>
+        <v>-15.8598999832852</v>
       </c>
       <c r="F14">
-        <v>1.054361622016356</v>
+        <v>0.3421296723545357</v>
       </c>
       <c r="G14">
-        <v>-9.602781416792853</v>
+        <v>-14.09480934557407</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-9.629305385591499</v>
       </c>
       <c r="E15">
-        <v>-17.92890541570169</v>
+        <v>-17.28883278556153</v>
       </c>
       <c r="F15">
-        <v>0.7391727954555611</v>
+        <v>1.222617952138186</v>
       </c>
       <c r="G15">
-        <v>-9.413348690490215</v>
+        <v>-13.41158392299759</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-9.973240074796092</v>
       </c>
       <c r="E16">
-        <v>-17.3077663353876</v>
+        <v>-18.10101912731122</v>
       </c>
       <c r="F16">
-        <v>1.724104950853784</v>
+        <v>1.087425078531696</v>
       </c>
       <c r="G16">
-        <v>-9.08132745726563</v>
+        <v>-13.96188928689956</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-10.34899510905345</v>
       </c>
       <c r="E17">
-        <v>-18.400215404998</v>
+        <v>-18.94551613110563</v>
       </c>
       <c r="F17">
-        <v>1.527886250683054</v>
+        <v>1.606483406595477</v>
       </c>
       <c r="G17">
-        <v>-9.207399652492155</v>
+        <v>-13.25046960323788</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-10.71461014686763</v>
       </c>
       <c r="E18">
-        <v>-18.96417797249124</v>
+        <v>-20.73014698126245</v>
       </c>
       <c r="F18">
-        <v>2.27799447147048</v>
+        <v>1.717317308355245</v>
       </c>
       <c r="G18">
-        <v>-8.592200974929391</v>
+        <v>-12.98894643727207</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-11.03685772476231</v>
       </c>
       <c r="E19">
-        <v>-20.37584370337633</v>
+        <v>-20.85990587547824</v>
       </c>
       <c r="F19">
-        <v>1.950658465315033</v>
+        <v>2.271463622866808</v>
       </c>
       <c r="G19">
-        <v>-8.229782312563216</v>
+        <v>-13.30970188402652</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-11.27082025474334</v>
       </c>
       <c r="E20">
-        <v>-21.20135734413059</v>
+        <v>-21.14686168792229</v>
       </c>
       <c r="F20">
-        <v>2.641069560852308</v>
+        <v>2.244289858585373</v>
       </c>
       <c r="G20">
-        <v>-8.478609536385918</v>
+        <v>-13.39769618446035</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-11.40190520182626</v>
       </c>
       <c r="E21">
-        <v>-21.81800417822907</v>
+        <v>-21.96822271801151</v>
       </c>
       <c r="F21">
-        <v>2.581420480911522</v>
+        <v>2.51163549743008</v>
       </c>
       <c r="G21">
-        <v>-8.38756953405596</v>
+        <v>-12.88629966228143</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-11.40313051731788</v>
       </c>
       <c r="E22">
-        <v>-21.34422164212457</v>
+        <v>-22.85861580587367</v>
       </c>
       <c r="F22">
-        <v>2.57791648679768</v>
+        <v>2.792457017183529</v>
       </c>
       <c r="G22">
-        <v>-8.469419461968901</v>
+        <v>-12.59339914569441</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-11.28534974478</v>
       </c>
       <c r="E23">
-        <v>-22.63618621956491</v>
+        <v>-23.01280581736083</v>
       </c>
       <c r="F23">
-        <v>2.813058514491153</v>
+        <v>2.73465353981618</v>
       </c>
       <c r="G23">
-        <v>-8.059232938016583</v>
+        <v>-12.48090680826998</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-11.05446828686542</v>
       </c>
       <c r="E24">
-        <v>-21.90963332130027</v>
+        <v>-22.79057548390842</v>
       </c>
       <c r="F24">
-        <v>2.916780053730485</v>
+        <v>2.762244801268626</v>
       </c>
       <c r="G24">
-        <v>-7.282545849048169</v>
+        <v>-12.70266370121806</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-10.74184450542118</v>
       </c>
       <c r="E25">
-        <v>-22.90806674203742</v>
+        <v>-23.50054511035697</v>
       </c>
       <c r="F25">
-        <v>3.05031453579657</v>
+        <v>2.90672698693011</v>
       </c>
       <c r="G25">
-        <v>-8.069823373196712</v>
+        <v>-12.94376742229764</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-10.38008504831668</v>
       </c>
       <c r="E26">
-        <v>-23.17070012058628</v>
+        <v>-23.25103977795635</v>
       </c>
       <c r="F26">
-        <v>2.712537786896239</v>
+        <v>2.309406163384637</v>
       </c>
       <c r="G26">
-        <v>-8.303057927529444</v>
+        <v>-12.15802930182486</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-10.00541973056962</v>
       </c>
       <c r="E27">
-        <v>-23.40919220420023</v>
+        <v>-22.3212082099614</v>
       </c>
       <c r="F27">
-        <v>2.758227219365048</v>
+        <v>2.747503174968406</v>
       </c>
       <c r="G27">
-        <v>-8.482078988111073</v>
+        <v>-12.03521799395451</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-9.661312638369349</v>
       </c>
       <c r="E28">
-        <v>-23.83602352179321</v>
+        <v>-22.26994588419457</v>
       </c>
       <c r="F28">
-        <v>2.305270953309861</v>
+        <v>2.74932723998937</v>
       </c>
       <c r="G28">
-        <v>-8.127532803037287</v>
+        <v>-12.57135091240287</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-9.372337660574962</v>
       </c>
       <c r="E29">
-        <v>-23.38717023510093</v>
+        <v>-22.35940135974209</v>
       </c>
       <c r="F29">
-        <v>2.522236943451108</v>
+        <v>2.502309737209363</v>
       </c>
       <c r="G29">
-        <v>-7.04729517248202</v>
+        <v>-11.98849295421324</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-9.177120814833215</v>
       </c>
       <c r="E30">
-        <v>-23.39957372540794</v>
+        <v>-22.33688578697596</v>
       </c>
       <c r="F30">
-        <v>2.229225168998061</v>
+        <v>2.085117405402642</v>
       </c>
       <c r="G30">
-        <v>-8.0066482326708</v>
+        <v>-11.70725880010661</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-9.076332640839224</v>
       </c>
       <c r="E31">
-        <v>-22.15642156929628</v>
+        <v>-22.15212857593701</v>
       </c>
       <c r="F31">
-        <v>2.543191325272324</v>
+        <v>2.159990221472079</v>
       </c>
       <c r="G31">
-        <v>-7.123450962067414</v>
+        <v>-11.05009895783359</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-9.08331090897499</v>
       </c>
       <c r="E32">
-        <v>-21.74541273988611</v>
+        <v>-21.91517164501165</v>
       </c>
       <c r="F32">
-        <v>2.30309566051011</v>
+        <v>1.994003618033919</v>
       </c>
       <c r="G32">
-        <v>-7.146700923389716</v>
+        <v>-11.61116690528373</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-9.172790882167103</v>
       </c>
       <c r="E33">
-        <v>-21.44990264004158</v>
+        <v>-21.65605689076676</v>
       </c>
       <c r="F33">
-        <v>2.619951162285338</v>
+        <v>2.172238461889872</v>
       </c>
       <c r="G33">
-        <v>-7.241591090181846</v>
+        <v>-11.30943385319793</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-9.325177898884556</v>
       </c>
       <c r="E34">
-        <v>-22.37283281364884</v>
+        <v>-20.92154293519664</v>
       </c>
       <c r="F34">
-        <v>2.334094825457673</v>
+        <v>2.362072106119824</v>
       </c>
       <c r="G34">
-        <v>-6.766173576923729</v>
+        <v>-10.95648997216515</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-9.503310786893973</v>
       </c>
       <c r="E35">
-        <v>-20.38722375855761</v>
+        <v>-21.05064520068131</v>
       </c>
       <c r="F35">
-        <v>2.905071908859317</v>
+        <v>2.020353985116972</v>
       </c>
       <c r="G35">
-        <v>-8.005790801376127</v>
+        <v>-11.28970300178388</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-9.671560424874622</v>
       </c>
       <c r="E36">
-        <v>-19.40670045252079</v>
+        <v>-19.92638812964104</v>
       </c>
       <c r="F36">
-        <v>2.656674345986246</v>
+        <v>2.335975219462028</v>
       </c>
       <c r="G36">
-        <v>-6.981623880619497</v>
+        <v>-11.21598377371539</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-9.800280203267912</v>
       </c>
       <c r="E37">
-        <v>-21.11095541751547</v>
+        <v>-19.33198063139423</v>
       </c>
       <c r="F37">
-        <v>3.128994528449273</v>
+        <v>2.351927918905141</v>
       </c>
       <c r="G37">
-        <v>-6.804559352451578</v>
+        <v>-10.05516746473426</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-9.855143440952023</v>
       </c>
       <c r="E38">
-        <v>-18.7821378458569</v>
+        <v>-19.37046360351141</v>
       </c>
       <c r="F38">
-        <v>2.914193890698944</v>
+        <v>2.358049554011829</v>
       </c>
       <c r="G38">
-        <v>-8.210068013876857</v>
+        <v>-10.90829505020445</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-9.824820818761927</v>
       </c>
       <c r="E39">
-        <v>-18.9159180249915</v>
+        <v>-19.53123801620573</v>
       </c>
       <c r="F39">
-        <v>2.737357331018917</v>
+        <v>2.306016483972381</v>
       </c>
       <c r="G39">
-        <v>-7.4196785769214</v>
+        <v>-10.1677955345258</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-9.688342777044712</v>
       </c>
       <c r="E40">
-        <v>-19.35802388541234</v>
+        <v>-18.84086762526238</v>
       </c>
       <c r="F40">
-        <v>2.282668120357074</v>
+        <v>2.123603354936708</v>
       </c>
       <c r="G40">
-        <v>-6.335362354261751</v>
+        <v>-10.77693260320616</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-9.455426294974766</v>
       </c>
       <c r="E41">
-        <v>-18.63656099193232</v>
+        <v>-17.12665454592483</v>
       </c>
       <c r="F41">
-        <v>2.560070139471767</v>
+        <v>2.26400168930239</v>
       </c>
       <c r="G41">
-        <v>-6.582173455851036</v>
+        <v>-10.6603914685872</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-9.126885560525876</v>
       </c>
       <c r="E42">
-        <v>-18.31172902288812</v>
+        <v>-16.68473435293831</v>
       </c>
       <c r="F42">
-        <v>2.836410191576071</v>
+        <v>2.348879526862839</v>
       </c>
       <c r="G42">
-        <v>-7.028146977082876</v>
+        <v>-10.18255725708542</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.727153901421211</v>
       </c>
       <c r="E43">
-        <v>-18.19770657584899</v>
+        <v>-17.63506179429197</v>
       </c>
       <c r="F43">
-        <v>2.58879957773566</v>
+        <v>2.134986779785979</v>
       </c>
       <c r="G43">
-        <v>-7.054399603209296</v>
+        <v>-9.967431386852494</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.277316765949999</v>
       </c>
       <c r="E44">
-        <v>-16.02778862864557</v>
+        <v>-16.89307585660919</v>
       </c>
       <c r="F44">
-        <v>2.350678740861719</v>
+        <v>2.071835362466155</v>
       </c>
       <c r="G44">
-        <v>-7.668389931650227</v>
+        <v>-9.820502754728562</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-7.806217820655427</v>
       </c>
       <c r="E45">
-        <v>-14.44690288104185</v>
+        <v>-16.39240324184715</v>
       </c>
       <c r="F45">
-        <v>2.847951006231874</v>
+        <v>1.785612887246453</v>
       </c>
       <c r="G45">
-        <v>-8.287577816587813</v>
+        <v>-9.786877543686185</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-7.343059248638736</v>
       </c>
       <c r="E46">
-        <v>-15.67045127317431</v>
+        <v>-15.81514507466739</v>
       </c>
       <c r="F46">
-        <v>2.383086130394041</v>
+        <v>1.923345535309927</v>
       </c>
       <c r="G46">
-        <v>-8.171695480531165</v>
+        <v>-9.324238736209653</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-6.906813340863184</v>
       </c>
       <c r="E47">
-        <v>-14.14526575586494</v>
+        <v>-15.88843389800753</v>
       </c>
       <c r="F47">
-        <v>2.439274291325932</v>
+        <v>1.47297211881667</v>
       </c>
       <c r="G47">
-        <v>-5.623108413124173</v>
+        <v>-10.0445240608255</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-6.523628588879006</v>
       </c>
       <c r="E48">
-        <v>-15.47564084983834</v>
+        <v>-14.68448926985428</v>
       </c>
       <c r="F48">
-        <v>2.452846262853399</v>
+        <v>1.762310912205703</v>
       </c>
       <c r="G48">
-        <v>-6.287289922485995</v>
+        <v>-9.980028012629422</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.196266899667018</v>
       </c>
       <c r="E49">
-        <v>-13.75345312777328</v>
+        <v>-14.02497590079919</v>
       </c>
       <c r="F49">
-        <v>2.468439450843697</v>
+        <v>1.799517862469846</v>
       </c>
       <c r="G49">
-        <v>-8.020794193760105</v>
+        <v>-10.5631772988265</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-5.942433029826308</v>
       </c>
       <c r="E50">
-        <v>-13.33649388351703</v>
+        <v>-13.38853510681318</v>
       </c>
       <c r="F50">
-        <v>2.307177855071106</v>
+        <v>1.804198138295663</v>
       </c>
       <c r="G50">
-        <v>-7.336610368250008</v>
+        <v>-10.2036818481715</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-5.754790297405481</v>
       </c>
       <c r="E51">
-        <v>-12.32073452122654</v>
+        <v>-13.69770308426485</v>
       </c>
       <c r="F51">
-        <v>2.533786041780939</v>
+        <v>1.142972083093819</v>
       </c>
       <c r="G51">
-        <v>-8.567004412829998</v>
+        <v>-10.32830071390629</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-5.638333542302751</v>
       </c>
       <c r="E52">
-        <v>-12.31026921779481</v>
+        <v>-12.48051266963917</v>
       </c>
       <c r="F52">
-        <v>2.551662210333352</v>
+        <v>1.207137422114669</v>
       </c>
       <c r="G52">
-        <v>-7.101022016038852</v>
+        <v>-10.98302730520795</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-5.583293055166182</v>
       </c>
       <c r="E53">
-        <v>-11.65953203136659</v>
+        <v>-11.70036528149375</v>
       </c>
       <c r="F53">
-        <v>2.147846355347038</v>
+        <v>1.383352706242597</v>
       </c>
       <c r="G53">
-        <v>-7.890186551144779</v>
+        <v>-10.37667440532612</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-5.582231147936111</v>
       </c>
       <c r="E54">
-        <v>-11.43600202587397</v>
+        <v>-12.00967817011367</v>
       </c>
       <c r="F54">
-        <v>2.275250918632408</v>
+        <v>1.36702889820303</v>
       </c>
       <c r="G54">
-        <v>-7.958393720890383</v>
+        <v>-10.49500654508183</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-5.627515087830027</v>
       </c>
       <c r="E55">
-        <v>-12.00315263906861</v>
+        <v>-11.97590481096446</v>
       </c>
       <c r="F55">
-        <v>2.105765291284823</v>
+        <v>1.132922329763056</v>
       </c>
       <c r="G55">
-        <v>-6.946184490621599</v>
+        <v>-10.58468591319515</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-5.703920955375131</v>
       </c>
       <c r="E56">
-        <v>-11.35174976696126</v>
+        <v>-10.87200775906267</v>
       </c>
       <c r="F56">
-        <v>2.385644128933886</v>
+        <v>1.042138232620647</v>
       </c>
       <c r="G56">
-        <v>-7.711195285473003</v>
+        <v>-10.58765216199834</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-5.810391744372042</v>
       </c>
       <c r="E57">
-        <v>-11.36557066963267</v>
+        <v>-11.18938585989025</v>
       </c>
       <c r="F57">
-        <v>2.430326266640892</v>
+        <v>1.077434967653934</v>
       </c>
       <c r="G57">
-        <v>-8.345439531523194</v>
+        <v>-10.82130715561456</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-5.930807884368728</v>
       </c>
       <c r="E58">
-        <v>-9.378381177112759</v>
+        <v>-10.85900651018665</v>
       </c>
       <c r="F58">
-        <v>2.31042505529008</v>
+        <v>0.8142261956188075</v>
       </c>
       <c r="G58">
-        <v>-7.978568185406701</v>
+        <v>-10.8519959127636</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-6.069798491842038</v>
       </c>
       <c r="E59">
-        <v>-9.733200701035754</v>
+        <v>-10.30494771534818</v>
       </c>
       <c r="F59">
-        <v>2.467185302595859</v>
+        <v>0.8143057188894762</v>
       </c>
       <c r="G59">
-        <v>-8.813345416952705</v>
+        <v>-11.38234530815484</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-6.217513933358374</v>
       </c>
       <c r="E60">
-        <v>-9.169541541301024</v>
+        <v>-10.47693462968549</v>
       </c>
       <c r="F60">
-        <v>1.833036921056725</v>
+        <v>1.029875081589603</v>
       </c>
       <c r="G60">
-        <v>-7.836698066866774</v>
+        <v>-11.17940224550644</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-6.378128826778193</v>
       </c>
       <c r="E61">
-        <v>-10.49225445725344</v>
+        <v>-10.23087999447873</v>
       </c>
       <c r="F61">
-        <v>1.996798529650965</v>
+        <v>1.101692878677514</v>
       </c>
       <c r="G61">
-        <v>-9.306318753205579</v>
+        <v>-11.31156253397969</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-6.548890583697622</v>
       </c>
       <c r="E62">
-        <v>-9.311771852933935</v>
+        <v>-10.235172987838</v>
       </c>
       <c r="F62">
-        <v>2.245678202352465</v>
+        <v>1.162051041115097</v>
       </c>
       <c r="G62">
-        <v>-8.797438245636508</v>
+        <v>-12.19535570278014</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-6.728265419887426</v>
       </c>
       <c r="E63">
-        <v>-9.273248124550683</v>
+        <v>-9.717930686681889</v>
       </c>
       <c r="F63">
-        <v>1.969119461253822</v>
+        <v>1.143371356181969</v>
       </c>
       <c r="G63">
-        <v>-9.511281248632937</v>
+        <v>-11.56736507725363</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.916459207599961</v>
       </c>
       <c r="E64">
-        <v>-8.771461505182755</v>
+        <v>-9.462407012325082</v>
       </c>
       <c r="F64">
-        <v>2.229230139202478</v>
+        <v>1.116457699265013</v>
       </c>
       <c r="G64">
-        <v>-9.036671508486402</v>
+        <v>-12.11457839162192</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-7.103433805331551</v>
       </c>
       <c r="E65">
-        <v>-7.696465174397919</v>
+        <v>-9.802287100496773</v>
       </c>
       <c r="F65">
-        <v>2.190508933326018</v>
+        <v>0.8186596179585904</v>
       </c>
       <c r="G65">
-        <v>-10.16504778172821</v>
+        <v>-12.10833470273486</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-7.290809985292455</v>
       </c>
       <c r="E66">
-        <v>-9.251534091683904</v>
+        <v>-9.372317550416488</v>
       </c>
       <c r="F66">
-        <v>1.791338562734603</v>
+        <v>0.8980039612683383</v>
       </c>
       <c r="G66">
-        <v>-9.71326425307495</v>
+        <v>-11.43487373422646</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-7.463489198463426</v>
       </c>
       <c r="E67">
-        <v>-9.337262633123112</v>
+        <v>-10.24907993151555</v>
       </c>
       <c r="F67">
-        <v>2.310156664251573</v>
+        <v>1.101270411302087</v>
       </c>
       <c r="G67">
-        <v>-9.851456355520748</v>
+        <v>-12.17477735170803</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-7.623185213107365</v>
       </c>
       <c r="E68">
-        <v>-8.976103245589378</v>
+        <v>-10.86508825077895</v>
       </c>
       <c r="F68">
-        <v>1.837400760534673</v>
+        <v>1.247106149299745</v>
       </c>
       <c r="G68">
-        <v>-9.787559516067274</v>
+        <v>-12.44344798549312</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-7.755631560896342</v>
       </c>
       <c r="E69">
-        <v>-8.156843427439711</v>
+        <v>-10.15813911649352</v>
       </c>
       <c r="F69">
-        <v>2.148701230506727</v>
+        <v>0.8975549861360209</v>
       </c>
       <c r="G69">
-        <v>-9.458845517836419</v>
+        <v>-11.38245786670318</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-7.859543783334092</v>
       </c>
       <c r="E70">
-        <v>-8.414450199840047</v>
+        <v>-9.258200005423195</v>
       </c>
       <c r="F70">
-        <v>1.527493604534127</v>
+        <v>0.5742846071935139</v>
       </c>
       <c r="G70">
-        <v>-9.462265311378486</v>
+        <v>-11.46463222807897</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-7.92597829508161</v>
       </c>
       <c r="E71">
-        <v>-9.999791965867308</v>
+        <v>-8.599922909772202</v>
       </c>
       <c r="F71">
-        <v>1.863794202722671</v>
+        <v>0.9191339569789481</v>
       </c>
       <c r="G71">
-        <v>-8.073276272194171</v>
+        <v>-11.63492338007354</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-7.951208354019393</v>
       </c>
       <c r="E72">
-        <v>-9.128848673868099</v>
+        <v>-9.86084026941595</v>
       </c>
       <c r="F72">
-        <v>2.238552585953584</v>
+        <v>1.083528438268927</v>
       </c>
       <c r="G72">
-        <v>-9.321934596514321</v>
+        <v>-12.27421951861666</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-7.933684527500771</v>
       </c>
       <c r="E73">
-        <v>-9.163813021681323</v>
+        <v>-10.28849576927832</v>
       </c>
       <c r="F73">
-        <v>1.801608661794512</v>
+        <v>1.01063210682257</v>
       </c>
       <c r="G73">
-        <v>-8.249122519603638</v>
+        <v>-12.39413409914014</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-7.868816117118596</v>
       </c>
       <c r="E74">
-        <v>-10.98416447481064</v>
+        <v>-10.19515486303222</v>
       </c>
       <c r="F74">
-        <v>1.97512843839373</v>
+        <v>0.6622779345558913</v>
       </c>
       <c r="G74">
-        <v>-9.268194510775331</v>
+        <v>-10.81472579108248</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-7.763360334863455</v>
       </c>
       <c r="E75">
-        <v>-10.16970483910911</v>
+        <v>-10.51365149693969</v>
       </c>
       <c r="F75">
-        <v>1.596002902215258</v>
+        <v>0.7063611626306727</v>
       </c>
       <c r="G75">
-        <v>-8.811723249638463</v>
+        <v>-10.79642840588693</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-7.612857510470485</v>
       </c>
       <c r="E76">
-        <v>-9.583693131672517</v>
+        <v>-11.64190721052873</v>
       </c>
       <c r="F76">
-        <v>1.636927565383165</v>
+        <v>0.6283330951239733</v>
       </c>
       <c r="G76">
-        <v>-9.84426585060945</v>
+        <v>-11.25119804661662</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-7.430281150832813</v>
       </c>
       <c r="E77">
-        <v>-9.57637964615013</v>
+        <v>-9.858965481176776</v>
       </c>
       <c r="F77">
-        <v>1.526912090617362</v>
+        <v>0.2572476929570731</v>
       </c>
       <c r="G77">
-        <v>-8.195187111677832</v>
+        <v>-11.39004563707919</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-7.213773738227058</v>
       </c>
       <c r="E78">
-        <v>-10.4645990664886</v>
+        <v>-11.72780783398023</v>
       </c>
       <c r="F78">
-        <v>1.799880687392272</v>
+        <v>0.4797877673517575</v>
       </c>
       <c r="G78">
-        <v>-8.941251654407987</v>
+        <v>-11.01821178319933</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-6.97641380586637</v>
       </c>
       <c r="E79">
-        <v>-11.24989532958074</v>
+        <v>-12.10463574158051</v>
       </c>
       <c r="F79">
-        <v>1.186878868911804</v>
+        <v>0.5445023139606633</v>
       </c>
       <c r="G79">
-        <v>-8.801794923566188</v>
+        <v>-10.72377186293655</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-6.719886444731182</v>
       </c>
       <c r="E80">
-        <v>-12.22785551932922</v>
+        <v>-11.89276202818363</v>
       </c>
       <c r="F80">
-        <v>1.124098560188435</v>
+        <v>0.2355278996556701</v>
       </c>
       <c r="G80">
-        <v>-9.085263695911824</v>
+        <v>-10.76268732575068</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-6.452729864659654</v>
       </c>
       <c r="E81">
-        <v>-12.62710390174147</v>
+        <v>-12.21943708614896</v>
       </c>
       <c r="F81">
-        <v>1.293174974039037</v>
+        <v>0.3333324105368049</v>
       </c>
       <c r="G81">
-        <v>-9.046510449829114</v>
+        <v>-10.66627099746495</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-6.180082162320375</v>
       </c>
       <c r="E82">
-        <v>-15.0218469980037</v>
+        <v>-13.83870617944168</v>
       </c>
       <c r="F82">
-        <v>1.249619415999839</v>
+        <v>0.2220221975204269</v>
       </c>
       <c r="G82">
-        <v>-7.709669123979399</v>
+        <v>-10.96626270259708</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-5.905107834538411</v>
       </c>
       <c r="E83">
-        <v>-14.80859210003448</v>
+        <v>-14.63318165934737</v>
       </c>
       <c r="F83">
-        <v>0.6028492003442493</v>
+        <v>0.2264241418989035</v>
       </c>
       <c r="G83">
-        <v>-6.975012721177573</v>
+        <v>-10.44239866591727</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-5.637645556669582</v>
       </c>
       <c r="E84">
-        <v>-14.55545493147972</v>
+        <v>-14.96360176531704</v>
       </c>
       <c r="F84">
-        <v>1.041473881963602</v>
+        <v>0.1489204309581762</v>
       </c>
       <c r="G84">
-        <v>-7.504114040900512</v>
+        <v>-10.25915997031861</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-5.376414192686005</v>
       </c>
       <c r="E85">
-        <v>-16.60987867759151</v>
+        <v>-16.0281010933521</v>
       </c>
       <c r="F85">
-        <v>0.7100656216559921</v>
+        <v>-0.4102731261386441</v>
       </c>
       <c r="G85">
-        <v>-7.22263159587844</v>
+        <v>-10.28540928589949</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-5.136009738609147</v>
       </c>
       <c r="E86">
-        <v>-16.77987306336545</v>
+        <v>-16.96964329513089</v>
       </c>
       <c r="F86">
-        <v>0.5492770236703997</v>
+        <v>-0.2184663107552242</v>
       </c>
       <c r="G86">
-        <v>-7.581948277074317</v>
+        <v>-9.738354877717086</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.914735364052341</v>
       </c>
       <c r="E87">
-        <v>-17.3813857373303</v>
+        <v>-18.91212769224708</v>
       </c>
       <c r="F87">
-        <v>0.5018181984292104</v>
+        <v>-0.1220236358842917</v>
       </c>
       <c r="G87">
-        <v>-7.761369913666197</v>
+        <v>-9.84662626957895</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-4.727332623910666</v>
       </c>
       <c r="E88">
-        <v>-19.31470450305497</v>
+        <v>-20.02856408867611</v>
       </c>
       <c r="F88">
-        <v>0.6764819504116945</v>
+        <v>-0.008870305396684859</v>
       </c>
       <c r="G88">
-        <v>-7.537040726834103</v>
+        <v>-10.25713722699412</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-4.576914964607058</v>
       </c>
       <c r="E89">
-        <v>-20.80729406445712</v>
+        <v>-20.56795515620373</v>
       </c>
       <c r="F89">
-        <v>0.5317686502448293</v>
+        <v>-0.3433352414206244</v>
       </c>
       <c r="G89">
-        <v>-7.650642097014194</v>
+        <v>-10.46124560167234</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-4.473923116804247</v>
       </c>
       <c r="E90">
-        <v>-21.59535269669394</v>
+        <v>-21.81768718504853</v>
       </c>
       <c r="F90">
-        <v>0.3051331274107041</v>
+        <v>-0.4943714699730583</v>
       </c>
       <c r="G90">
-        <v>-7.89958187938523</v>
+        <v>-10.03724086063911</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-4.426849267305333</v>
       </c>
       <c r="E91">
-        <v>-24.55698375465837</v>
+        <v>-24.31716029968615</v>
       </c>
       <c r="F91">
-        <v>0.4009586685665509</v>
+        <v>-0.3167637002410247</v>
       </c>
       <c r="G91">
-        <v>-7.494033429733431</v>
+        <v>-10.54320477758808</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-4.439062133092178</v>
       </c>
       <c r="E92">
-        <v>-27.89782469755111</v>
+        <v>-25.88166655680413</v>
       </c>
       <c r="F92">
-        <v>0.2087575502993985</v>
+        <v>-0.7230041866153331</v>
       </c>
       <c r="G92">
-        <v>-7.46760203414789</v>
+        <v>-10.13374988419994</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.522599803983736</v>
       </c>
       <c r="E93">
-        <v>-27.60079303043999</v>
+        <v>-27.94240299568261</v>
       </c>
       <c r="F93">
-        <v>0.01127558983939912</v>
+        <v>-0.9078419470390008</v>
       </c>
       <c r="G93">
-        <v>-7.192912828572402</v>
+        <v>-9.265536142707296</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.672174360756823</v>
       </c>
       <c r="E94">
-        <v>-30.1075162319639</v>
+        <v>-30.66352906333668</v>
       </c>
       <c r="F94">
-        <v>-0.1311845509918514</v>
+        <v>-0.6293671921376826</v>
       </c>
       <c r="G94">
-        <v>-7.854482317503739</v>
+        <v>-9.81528533495867</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.896544507606728</v>
       </c>
       <c r="E95">
-        <v>-31.60733097364529</v>
+        <v>-33.34542948913629</v>
       </c>
       <c r="F95">
-        <v>0.3091117760463502</v>
+        <v>-0.7064360101919401</v>
       </c>
       <c r="G95">
-        <v>-9.163379328456466</v>
+        <v>-9.830305280070343</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-5.190282822363846</v>
       </c>
       <c r="E96">
-        <v>-35.00375440650818</v>
+        <v>-34.03698181179565</v>
       </c>
       <c r="F96">
-        <v>0.3302351448177376</v>
+        <v>-0.6737767969691668</v>
       </c>
       <c r="G96">
-        <v>-7.685329993174677</v>
+        <v>-10.60838279816525</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-5.549417773788394</v>
       </c>
       <c r="E97">
-        <v>-38.16181028879231</v>
+        <v>-38.32631163559494</v>
       </c>
       <c r="F97">
-        <v>-0.4928389902778792</v>
+        <v>-0.8937572160892008</v>
       </c>
       <c r="G97">
-        <v>-8.256071354690569</v>
+        <v>-10.53787148872431</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-5.979862332553445</v>
       </c>
       <c r="E98">
-        <v>-39.79120052149218</v>
+        <v>-39.2635268804594</v>
       </c>
       <c r="F98">
-        <v>-0.1697202025700845</v>
+        <v>-0.8829279690324028</v>
       </c>
       <c r="G98">
-        <v>-7.422667999543362</v>
+        <v>-10.49425836178995</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-6.454422035489984</v>
       </c>
       <c r="E99">
-        <v>-43.44190682683377</v>
+        <v>-42.23905356091637</v>
       </c>
       <c r="F99">
-        <v>-0.7190951208415222</v>
+        <v>-0.9490755912481518</v>
       </c>
       <c r="G99">
-        <v>-8.134173757389064</v>
+        <v>-11.16353149019118</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-6.998050594162443</v>
       </c>
       <c r="E100">
-        <v>-44.34709217504198</v>
+        <v>-44.42283090282027</v>
       </c>
       <c r="F100">
-        <v>-0.9612351963538457</v>
+        <v>-1.013504351103092</v>
       </c>
       <c r="G100">
-        <v>-7.831738869648945</v>
+        <v>-10.77592288681669</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-7.53809888241492</v>
       </c>
       <c r="E101">
-        <v>-48.24183794465692</v>
+        <v>-46.88769968332828</v>
       </c>
       <c r="F101">
-        <v>-1.013114190056373</v>
+        <v>-0.9867282031750004</v>
       </c>
       <c r="G101">
-        <v>-8.83576443134465</v>
+        <v>-10.44813915188237</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-8.153608312472848</v>
       </c>
       <c r="E102">
-        <v>-49.52860949452896</v>
+        <v>-49.56371762139193</v>
       </c>
       <c r="F102">
-        <v>-0.6598859039916219</v>
+        <v>-1.431182934575256</v>
       </c>
       <c r="G102">
-        <v>-8.124602970235031</v>
+        <v>-11.10029344930002</v>
       </c>
     </row>
   </sheetData>
